--- a/AfterToken/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1040,53 +1040,53 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>cfg.UnlockContentType</t>
         </is>
       </c>
-      <c r="C29" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="C29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr">
         <is>
           <t>解锁内容类型</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="0" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="J30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t>关卡</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="0" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="J31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t>武器</t>
         </is>

--- a/AfterToken/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/__enums__.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -1092,6 +1092,194 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>cfg.ESkillEffect</t>
+        </is>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>技能效果类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>DamagePct</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>伤害百分比(每级小数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>MaxHpAdd</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>生命上限加算</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>StaminaMaxAdd</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>耐力上限加算</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>MoveSpeedPct</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>移速百分比</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ReloadTimePct</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>换弹时间缩减百分比</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ClipSizeAdd</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>弹匣容量加算</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>GoldGainPct</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>金币获取百分比</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ExpGainPct</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>8</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>经验获取百分比</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ProductionSpeedPct</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>9</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>生产加速百分比</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>DodgeCostPct</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>10</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>闪避耐力消耗缩减百分比</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
